--- a/spec/fixtures/files/import_assessment_questions/invalid_rows.xlsx
+++ b/spec/fixtures/files/import_assessment_questions/invalid_rows.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohanpujari/tte/psychometrics/spec/fixtures/files/import_assessment_questions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohan-pujari/tte/psychometrics/spec/fixtures/files/import_assessment_questions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA0F23D-3DAD-294F-94B7-3CD101D342DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204C9045-2F95-F94D-9004-E7A1C5E797BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="35120" windowHeight="22500" xr2:uid="{076B2D0F-1935-5E46-9497-2286E1A2EE28}"/>
   </bookViews>
@@ -83,9 +83,6 @@
     <t>TextEntry</t>
   </si>
   <si>
-    <t>Accountability</t>
-  </si>
-  <si>
     <t>scalePointsTexts</t>
   </si>
   <si>
@@ -101,7 +98,10 @@
     <t>WrongType</t>
   </si>
   <si>
-    <t>a,b</t>
+    <t>Accountability: a,b</t>
+  </si>
+  <si>
+    <t>Factors</t>
   </si>
 </sst>
 </file>
@@ -498,7 +498,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
@@ -575,13 +575,13 @@
         <v>7</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M2" t="s">
         <v>8</v>
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -604,19 +604,19 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="M3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" t="s">
         <v>19</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>20</v>
-      </c>
-      <c r="P3" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
